--- a/data/Sizing/Fork data.xlsx
+++ b/data/Sizing/Fork data.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/Sizing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D96EE657-BD11-8D48-B6E7-01609346B39F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0144E6-160B-FB47-8E3F-711258FDABFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30580" yWindow="-17300" windowWidth="27640" windowHeight="16440" xr2:uid="{7C5FB5DD-0678-0A44-B500-626A7C5158D9}"/>
+    <workbookView xWindow="32120" yWindow="-17980" windowWidth="27640" windowHeight="16440" xr2:uid="{7C5FB5DD-0678-0A44-B500-626A7C5158D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>Fork</t>
   </si>
@@ -54,6 +54,18 @@
   </si>
   <si>
     <t>Fox 34 SC 120 mm</t>
+  </si>
+  <si>
+    <t>Enve Gravel Disc (G series)</t>
+  </si>
+  <si>
+    <t>Travel</t>
+  </si>
+  <si>
+    <t>47, 50</t>
+  </si>
+  <si>
+    <t>Enve Adventure</t>
   </si>
 </sst>
 </file>
@@ -432,77 +444,129 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{575F23C2-FDDA-F54D-85AF-8D9D6DE0AEFD}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="1" width="31" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2">
+      <c r="E1" s="2">
         <v>0.2</v>
       </c>
-      <c r="E1" s="2">
+      <c r="F1" s="2">
         <v>0.25</v>
       </c>
-      <c r="F1" s="2">
+      <c r="G1" s="2">
         <v>0.3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1">
+        <v>100</v>
+      </c>
+      <c r="C2" s="1">
         <v>503.7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="1">
-        <f>$B2-D1*100</f>
+      <c r="E2" s="1">
+        <f>$C2-E1*100</f>
         <v>483.7</v>
       </c>
-      <c r="E2" s="1">
-        <f t="shared" ref="E2:F2" si="0">$B2-E1*100</f>
+      <c r="F2" s="1">
+        <f t="shared" ref="F2:G2" si="0">$C2-F1*100</f>
         <v>478.7</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G2" s="1">
         <f t="shared" si="0"/>
         <v>473.7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="1">
+        <v>120</v>
+      </c>
+      <c r="C3" s="1">
         <v>530</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="1">
-        <f>$B3 - D1*120</f>
+      <c r="E3" s="1">
+        <f>$C3 - E1*120</f>
         <v>506</v>
       </c>
-      <c r="E3" s="1">
-        <f t="shared" ref="E3:F3" si="1">$B3 - E1*120</f>
+      <c r="F3" s="1">
+        <f t="shared" ref="F3:G3" si="1">$C3 - F1*120</f>
         <v>500</v>
       </c>
-      <c r="F3" s="1">
+      <c r="G3" s="1">
         <f t="shared" si="1"/>
         <v>494</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1">
+        <v>395</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1">
+        <v>398</v>
+      </c>
+      <c r="D5" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1">
+        <v>406</v>
+      </c>
+      <c r="D6" s="1">
+        <v>55.5</v>
       </c>
     </row>
   </sheetData>
